--- a/artfynd/A 10723-2024 artfynd.xlsx
+++ b/artfynd/A 10723-2024 artfynd.xlsx
@@ -7146,7 +7146,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117049556</v>
+        <v>117049551</v>
       </c>
       <c r="B63" t="n">
         <v>57287</v>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467434</v>
+        <v>467194</v>
       </c>
       <c r="R63" t="n">
-        <v>7078786</v>
+        <v>7078713</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7253,7 +7253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117049544</v>
+        <v>117049552</v>
       </c>
       <c r="B64" t="n">
         <v>57287</v>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467390</v>
+        <v>467240</v>
       </c>
       <c r="R64" t="n">
-        <v>7078229</v>
+        <v>7078733</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7360,7 +7360,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117049550</v>
+        <v>117049556</v>
       </c>
       <c r="B65" t="n">
         <v>57287</v>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467238</v>
+        <v>467434</v>
       </c>
       <c r="R65" t="n">
-        <v>7078683</v>
+        <v>7078786</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7467,7 +7467,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117049547</v>
+        <v>117049549</v>
       </c>
       <c r="B66" t="n">
         <v>57287</v>
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467301</v>
+        <v>467232</v>
       </c>
       <c r="R66" t="n">
-        <v>7078571</v>
+        <v>7078676</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7574,7 +7574,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117049543</v>
+        <v>117049544</v>
       </c>
       <c r="B67" t="n">
         <v>57287</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467588</v>
+        <v>467390</v>
       </c>
       <c r="R67" t="n">
-        <v>7078462</v>
+        <v>7078229</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7681,7 +7681,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117049549</v>
+        <v>117049543</v>
       </c>
       <c r="B68" t="n">
         <v>57287</v>
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467232</v>
+        <v>467588</v>
       </c>
       <c r="R68" t="n">
-        <v>7078676</v>
+        <v>7078462</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117049558</v>
+        <v>117049550</v>
       </c>
       <c r="B69" t="n">
         <v>57287</v>
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467446</v>
+        <v>467238</v>
       </c>
       <c r="R69" t="n">
-        <v>7078785</v>
+        <v>7078683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7895,7 +7895,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117049552</v>
+        <v>117049553</v>
       </c>
       <c r="B70" t="n">
         <v>57287</v>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>467240</v>
+        <v>467238</v>
       </c>
       <c r="R70" t="n">
-        <v>7078733</v>
+        <v>7078741</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8002,7 +8002,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117049553</v>
+        <v>117049558</v>
       </c>
       <c r="B71" t="n">
         <v>57287</v>
@@ -8042,10 +8042,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>467238</v>
+        <v>467446</v>
       </c>
       <c r="R71" t="n">
-        <v>7078741</v>
+        <v>7078785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8109,7 +8109,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117049551</v>
+        <v>117049547</v>
       </c>
       <c r="B72" t="n">
         <v>57287</v>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>467194</v>
+        <v>467301</v>
       </c>
       <c r="R72" t="n">
-        <v>7078713</v>
+        <v>7078571</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 10723-2024 artfynd.xlsx
+++ b/artfynd/A 10723-2024 artfynd.xlsx
@@ -7149,7 +7149,7 @@
         <v>117049551</v>
       </c>
       <c r="B63" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7253,10 +7253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117049552</v>
+        <v>117049549</v>
       </c>
       <c r="B64" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467240</v>
+        <v>467232</v>
       </c>
       <c r="R64" t="n">
-        <v>7078733</v>
+        <v>7078676</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7360,10 +7360,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117049556</v>
+        <v>117049552</v>
       </c>
       <c r="B65" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467434</v>
+        <v>467240</v>
       </c>
       <c r="R65" t="n">
-        <v>7078786</v>
+        <v>7078733</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7467,10 +7467,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117049549</v>
+        <v>117049550</v>
       </c>
       <c r="B66" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467232</v>
+        <v>467238</v>
       </c>
       <c r="R66" t="n">
-        <v>7078676</v>
+        <v>7078683</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7574,10 +7574,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117049544</v>
+        <v>117049543</v>
       </c>
       <c r="B67" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467390</v>
+        <v>467588</v>
       </c>
       <c r="R67" t="n">
-        <v>7078229</v>
+        <v>7078462</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7681,10 +7681,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117049543</v>
+        <v>117049544</v>
       </c>
       <c r="B68" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467588</v>
+        <v>467390</v>
       </c>
       <c r="R68" t="n">
-        <v>7078462</v>
+        <v>7078229</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7788,10 +7788,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117049550</v>
+        <v>117049547</v>
       </c>
       <c r="B69" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467238</v>
+        <v>467301</v>
       </c>
       <c r="R69" t="n">
-        <v>7078683</v>
+        <v>7078571</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7898,7 +7898,7 @@
         <v>117049553</v>
       </c>
       <c r="B70" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>117049558</v>
       </c>
       <c r="B71" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117049547</v>
+        <v>117049556</v>
       </c>
       <c r="B72" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>467301</v>
+        <v>467434</v>
       </c>
       <c r="R72" t="n">
-        <v>7078571</v>
+        <v>7078786</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
